--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_218_R22.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_218_R22.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4006</v>
+        <v>1.8566</v>
       </c>
       <c r="E2" t="n">
-        <v>2.3811</v>
+        <v>1.7362</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0195</v>
+        <v>0.1203</v>
       </c>
       <c r="G2" t="n">
         <v>-0.4178</v>
@@ -610,13 +610,13 @@
         <v>3.2473</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8184</v>
+        <v>0.2743</v>
       </c>
       <c r="T2" t="n">
-        <v>1.404</v>
+        <v>0.7591</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5856</v>
+        <v>-0.4848</v>
       </c>
       <c r="V2" t="n">
         <v>1.0722</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. ATAMNA</t>
+          <t>S. HARRISON</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2541</v>
+        <v>1.3454</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5122</v>
+        <v>0.6616</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7419</v>
+        <v>0.6838</v>
       </c>
       <c r="G3" t="n">
-        <v>1.2317</v>
+        <v>0.926</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0263</v>
+        <v>0.1164</v>
       </c>
       <c r="I3" t="n">
-        <v>1.258</v>
+        <v>0.8096</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9603</v>
+        <v>1.9167</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0168</v>
+        <v>1.3682</v>
       </c>
       <c r="L3" t="n">
-        <v>0.9435</v>
+        <v>0.5486</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2714</v>
+        <v>-0.9908</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0431</v>
+        <v>-1.2518</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3145</v>
+        <v>0.261</v>
       </c>
       <c r="P3" t="n">
-        <v>0.232</v>
+        <v>1.1598</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R3" t="n">
-        <v>0.232</v>
+        <v>2.3195</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2095</v>
+        <v>-0.3459</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4481</v>
+        <v>0.2989</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2385</v>
+        <v>-0.6449</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>-0.3943</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>-0.3943</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. LIGHTY</t>
+          <t>A. ATAMNA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.502</v>
+        <v>1.2877</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.4939</v>
+        <v>0.5122</v>
       </c>
       <c r="F4" t="n">
-        <v>0.996</v>
+        <v>0.7755</v>
       </c>
       <c r="G4" t="n">
-        <v>1.6322</v>
+        <v>1.2317</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.3155</v>
+        <v>-0.0263</v>
       </c>
       <c r="I4" t="n">
-        <v>2.9478</v>
+        <v>1.258</v>
       </c>
       <c r="J4" t="n">
-        <v>1.8686</v>
+        <v>0.9603</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.3998</v>
+        <v>0.0168</v>
       </c>
       <c r="L4" t="n">
-        <v>2.2685</v>
+        <v>0.9435</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2364</v>
+        <v>0.2714</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.9157</v>
+        <v>-0.0431</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6793</v>
+        <v>0.3145</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.3917</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9278</v>
+        <v>0.232</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5245</v>
+        <v>-0.1759</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9709</v>
+        <v>-0.4481</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4463</v>
+        <v>0.2721</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. HARRISON</t>
+          <t>D. LIGHTY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4719</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0775</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5494</v>
+        <v>0.9287</v>
       </c>
       <c r="G5" t="n">
-        <v>0.926</v>
+        <v>1.6322</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1164</v>
+        <v>-1.3155</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8096</v>
+        <v>2.9478</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9167</v>
+        <v>1.8686</v>
       </c>
       <c r="K5" t="n">
-        <v>1.3682</v>
+        <v>-0.3998</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5486</v>
+        <v>2.2685</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.9908</v>
+        <v>-0.2364</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.2518</v>
+        <v>-0.9157</v>
       </c>
       <c r="O5" t="n">
-        <v>0.261</v>
+        <v>0.6793</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1598</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1598</v>
+        <v>-1.3917</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3195</v>
+        <v>0.9278</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.2195</v>
+        <v>-0.0885</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4402</v>
+        <v>-0.4676</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.7793</v>
+        <v>0.3791</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3943</v>
+        <v>-0.1418</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.3943</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B. VAUTIER</t>
+          <t>G. WATSON</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3651</v>
+        <v>0.507</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8774</v>
+        <v>0.1896</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5123</v>
+        <v>0.3174</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5226</v>
+        <v>3.266</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0228</v>
+        <v>-0.0866</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5454</v>
+        <v>3.3525</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5981</v>
+        <v>4.5214</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5244</v>
+        <v>1.691</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0736</v>
+        <v>2.8305</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0755</v>
+        <v>-1.2555</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5473</v>
+        <v>-1.7775</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4718</v>
+        <v>0.5221</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.4639</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1598</v>
+        <v>-4.871</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6959</v>
+        <v>3.2473</v>
       </c>
       <c r="S6" t="n">
-        <v>1.5204</v>
+        <v>0.3312</v>
       </c>
       <c r="T6" t="n">
-        <v>1.4391</v>
+        <v>0.3973</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0813</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.214</v>
+        <v>-1.4665</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.214</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. WATSON</t>
+          <t>B. VAUTIER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0567</v>
+        <v>-0.3955</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2271</v>
+        <v>0.0832</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2838</v>
+        <v>-0.4787</v>
       </c>
       <c r="G7" t="n">
-        <v>3.266</v>
+        <v>0.5226</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0866</v>
+        <v>-0.0228</v>
       </c>
       <c r="I7" t="n">
-        <v>3.3525</v>
+        <v>0.5454</v>
       </c>
       <c r="J7" t="n">
-        <v>4.5214</v>
+        <v>0.5981</v>
       </c>
       <c r="K7" t="n">
-        <v>1.691</v>
+        <v>0.5244</v>
       </c>
       <c r="L7" t="n">
-        <v>2.8305</v>
+        <v>0.0736</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2555</v>
+        <v>-0.0755</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.7775</v>
+        <v>-0.5473</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5221</v>
+        <v>0.4718</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.6237</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.871</v>
+        <v>-1.1598</v>
       </c>
       <c r="R7" t="n">
-        <v>3.2473</v>
+        <v>0.6959</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1191</v>
+        <v>0.7598</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0193</v>
+        <v>0.6449</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0997</v>
+        <v>0.1149</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.4665</v>
+        <v>-1.214</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.6083</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Z. SELJAAS</t>
+          <t>M. NDIAYE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5632</v>
+        <v>-0.4608</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1872</v>
+        <v>-1.1039</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3759</v>
+        <v>0.6431</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3298</v>
+        <v>-1.9036</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0216</v>
+        <v>-0.7993</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3513</v>
+        <v>-1.1043</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0368</v>
+        <v>-0.8054</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>0.9782</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0368</v>
+        <v>-1.7836</v>
       </c>
       <c r="M8" t="n">
-        <v>0.293</v>
+        <v>-1.0982</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0216</v>
+        <v>-1.7775</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3145</v>
+        <v>0.6793</v>
       </c>
       <c r="P8" t="n">
-        <v>0.232</v>
+        <v>2.0876</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="R8" t="n">
-        <v>0.232</v>
+        <v>2.3195</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0527</v>
+        <v>0.4274</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.224</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1713</v>
+        <v>0.494</v>
       </c>
       <c r="V8" t="n">
         <v>-1.0722</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. NDIAYE</t>
+          <t>Z. SELJAAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7183</v>
+        <v>-0.6304</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.0671</v>
+        <v>-0.1872</v>
       </c>
       <c r="F9" t="n">
-        <v>1.3488</v>
+        <v>-0.4432</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.9036</v>
+        <v>0.3298</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.7993</v>
+        <v>-0.0216</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.1043</v>
+        <v>0.3513</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.8054</v>
+        <v>0.0368</v>
       </c>
       <c r="K9" t="n">
-        <v>0.9782</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.7836</v>
+        <v>0.0368</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.0982</v>
+        <v>0.293</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.7775</v>
+        <v>-0.0216</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6793</v>
+        <v>0.3145</v>
       </c>
       <c r="P9" t="n">
-        <v>2.0876</v>
+        <v>0.232</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.3195</v>
+        <v>0.232</v>
       </c>
       <c r="S9" t="n">
-        <v>0.17</v>
+        <v>-0.1199</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0297</v>
+        <v>-0.224</v>
       </c>
       <c r="U9" t="n">
-        <v>1.1997</v>
+        <v>0.1041</v>
       </c>
       <c r="V9" t="n">
         <v>-1.0722</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. TRAORE</t>
+          <t>T. HEURTEL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.0608</v>
+        <v>-2.734</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.3239</v>
+        <v>-4.4865</v>
       </c>
       <c r="F10" t="n">
-        <v>1.2631</v>
+        <v>1.7525</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.248</v>
+        <v>-1.5943</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3168</v>
+        <v>-0.9049</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.9312</v>
+        <v>-0.6894</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.1107</v>
+        <v>-0.7716</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9243</v>
+        <v>0.3361</v>
       </c>
       <c r="L10" t="n">
-        <v>-3.035</v>
+        <v>-1.1077</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.1373</v>
+        <v>-0.8227</v>
       </c>
       <c r="N10" t="n">
         <v>-1.241</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1038</v>
+        <v>0.4183</v>
       </c>
       <c r="P10" t="n">
-        <v>0.232</v>
+        <v>-2.0876</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.5515</v>
+        <v>-3.4793</v>
       </c>
       <c r="R10" t="n">
-        <v>2.7834</v>
+        <v>1.3917</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0448</v>
+        <v>0.1592</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3383</v>
+        <v>-0.2357</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3831</v>
+        <v>0.3949</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.7886</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>0.7886</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B. MASSA</t>
+          <t>A. TRAORE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0699</v>
+        <v>-3.0101</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1923</v>
+        <v>-4.2059</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8776</v>
+        <v>1.1959</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.8566</v>
+        <v>-3.248</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.9135</v>
+        <v>-0.3168</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0569</v>
+        <v>-2.9312</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.4455</v>
+        <v>-2.1107</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.5559</v>
+        <v>0.9243</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1104</v>
+        <v>-3.035</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.4112</v>
+        <v>-1.1373</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3577</v>
+        <v>-1.241</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.0535</v>
+        <v>0.1038</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1598</v>
+        <v>-2.5515</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6959</v>
+        <v>2.7834</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3229</v>
+        <v>0.0059</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4129</v>
+        <v>0.4562</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0901</v>
+        <v>-0.4503</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>T. HEURTEL</t>
+          <t>B. MASSA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.5135</v>
+        <v>-3.3662</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.0644</v>
+        <v>-2.5894</v>
       </c>
       <c r="F12" t="n">
-        <v>1.5509</v>
+        <v>-0.7768</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.5943</v>
+        <v>-1.8566</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.9049</v>
+        <v>-1.9135</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6894</v>
+        <v>0.0569</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.7716</v>
+        <v>-1.4455</v>
       </c>
       <c r="K12" t="n">
-        <v>0.3361</v>
+        <v>-1.5559</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.1077</v>
+        <v>0.1104</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.8227</v>
+        <v>-0.4112</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.241</v>
+        <v>-0.3577</v>
       </c>
       <c r="O12" t="n">
-        <v>0.4183</v>
+        <v>-0.0535</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.0876</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.4793</v>
+        <v>-1.1598</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3917</v>
+        <v>0.6959</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6203</v>
+        <v>0.0266</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8136</v>
+        <v>0.0158</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1933</v>
+        <v>0.0108</v>
       </c>
       <c r="V12" t="n">
-        <v>0.7886</v>
+        <v>-1.0722</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0.7886</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.0896</v>
+        <v>-4.4355</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.6963</v>
+        <v>-3.311</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.3933</v>
+        <v>-1.1245</v>
       </c>
       <c r="G13" t="n">
         <v>-1.4858</v>
@@ -1468,13 +1468,13 @@
         <v>1.6237</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.122</v>
+        <v>-0.4679</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7468</v>
+        <v>-0.3615</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3752</v>
+        <v>-0.1063</v>
       </c>
       <c r="V13" t="n">
         <v>-0.3943</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-10.9649</v>
+        <v>-9.097799999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-14.559</v>
+        <v>-12.6918</v>
       </c>
       <c r="F14" t="n">
-        <v>3.594299999999999</v>
+        <v>3.594</v>
       </c>
       <c r="G14" t="n">
         <v>-2.5978</v>
@@ -1516,10 +1516,10 @@
         <v>-6.8297</v>
       </c>
       <c r="I14" t="n">
-        <v>4.2319</v>
+        <v>4.231899999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>6.004700000000001</v>
+        <v>6.0047</v>
       </c>
       <c r="K14" t="n">
         <v>5.6884</v>
@@ -1546,22 +1546,22 @@
         <v>19.716</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.0807</v>
+        <v>0.7863</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.0983</v>
+        <v>0.7687000000000002</v>
       </c>
       <c r="U14" t="n">
-        <v>0.01739999999999997</v>
+        <v>0.01749999999999971</v>
       </c>
       <c r="V14" t="n">
-        <v>-4.966699999999999</v>
+        <v>-4.9667</v>
       </c>
       <c r="W14" t="n">
         <v>2.5698</v>
       </c>
       <c r="X14" t="n">
-        <v>-7.536500000000001</v>
+        <v>-7.5365</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.8625</v>
+        <v>4.3476</v>
       </c>
       <c r="E15" t="n">
         <v>2.6916</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1709</v>
+        <v>1.656</v>
       </c>
       <c r="G15" t="n">
         <v>2.2914</v>
@@ -1624,13 +1624,13 @@
         <v>3.4793</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2696</v>
+        <v>0.7547</v>
       </c>
       <c r="T15" t="n">
         <v>-0.1098</v>
       </c>
       <c r="U15" t="n">
-        <v>1.3794</v>
+        <v>0.8646</v>
       </c>
       <c r="V15" t="n">
         <v>0.1418</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T. ODIASE</t>
+          <t>E. BRYANT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.9207</v>
+        <v>4.2407</v>
       </c>
       <c r="E16" t="n">
-        <v>2.4652</v>
+        <v>1.7983</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4555</v>
+        <v>2.4423</v>
       </c>
       <c r="G16" t="n">
-        <v>1.0615</v>
+        <v>3.453</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9075</v>
+        <v>5.2397</v>
       </c>
       <c r="I16" t="n">
-        <v>0.154</v>
+        <v>-1.7866</v>
       </c>
       <c r="J16" t="n">
-        <v>1.1294</v>
+        <v>4.7254</v>
       </c>
       <c r="K16" t="n">
-        <v>1.1294</v>
+        <v>6.1877</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>-1.4623</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.0679</v>
+        <v>-1.2724</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.222</v>
+        <v>-0.9481000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>0.154</v>
+        <v>-0.3243</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9278</v>
+        <v>-0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-3.4793</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9278</v>
+        <v>3.4793</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8593</v>
+        <v>0.2515</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2636</v>
+        <v>0.016</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5957</v>
+        <v>0.2355</v>
       </c>
       <c r="V16" t="n">
-        <v>1.0722</v>
+        <v>0.5361</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0722</v>
+        <v>0.5361</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E. BRYANT</t>
+          <t>T. ODIASE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.8645</v>
+        <v>3.5568</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7367</v>
+        <v>2.3472</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1278</v>
+        <v>1.2095</v>
       </c>
       <c r="G17" t="n">
-        <v>3.453</v>
+        <v>1.0615</v>
       </c>
       <c r="H17" t="n">
-        <v>5.2397</v>
+        <v>0.9075</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.7866</v>
+        <v>0.154</v>
       </c>
       <c r="J17" t="n">
-        <v>4.7254</v>
+        <v>1.1294</v>
       </c>
       <c r="K17" t="n">
-        <v>6.1877</v>
+        <v>1.1294</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.4623</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.2724</v>
+        <v>-0.0679</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.9481000000000001</v>
+        <v>-0.222</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3243</v>
+        <v>0.154</v>
       </c>
       <c r="P17" t="n">
-        <v>-0</v>
+        <v>0.9278</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.4793</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>3.4793</v>
+        <v>0.9278</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1246</v>
+        <v>0.4953</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.0455</v>
+        <v>0.1456</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0791</v>
+        <v>0.3497</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5361</v>
+        <v>1.0722</v>
       </c>
       <c r="W17" t="n">
-        <v>0.5361</v>
+        <v>1.0722</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. MALCOLM</t>
+          <t>I. WAINRIGHT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.9397</v>
+        <v>1.5904</v>
       </c>
       <c r="E18" t="n">
-        <v>1.164</v>
+        <v>-0.0015</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7756999999999999</v>
+        <v>1.5919</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.885</v>
+        <v>-0.2026</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6709000000000001</v>
+        <v>-1.3336</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.214</v>
+        <v>1.131</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2017</v>
+        <v>-0.0882</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2017</v>
+        <v>-1.0685</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.9802999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.0866</v>
+        <v>-0.1143</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8726</v>
+        <v>-0.2651</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.214</v>
+        <v>0.1507</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1598</v>
+        <v>2.0876</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3195</v>
+        <v>2.0876</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7345</v>
+        <v>0.3833</v>
       </c>
       <c r="T18" t="n">
-        <v>1.0499</v>
+        <v>0.0868</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3154</v>
+        <v>0.2965</v>
       </c>
       <c r="V18" t="n">
-        <v>0.9304</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1418</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>I. WAINRIGHT</t>
+          <t>J. MOTLEY</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.6868</v>
+        <v>1.5885</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5883</v>
+        <v>-0.175</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0985</v>
+        <v>1.7635</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2026</v>
+        <v>-1.2773</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.3336</v>
+        <v>-0.0495</v>
       </c>
       <c r="I19" t="n">
-        <v>1.131</v>
+        <v>-1.2279</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.0882</v>
+        <v>-0.0837</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.0685</v>
+        <v>0.6659</v>
       </c>
       <c r="L19" t="n">
-        <v>0.9802999999999999</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1143</v>
+        <v>-1.1937</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2651</v>
+        <v>-0.7153</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1507</v>
+        <v>-0.4783</v>
       </c>
       <c r="P19" t="n">
-        <v>2.0876</v>
+        <v>1.6237</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R19" t="n">
-        <v>2.0876</v>
+        <v>2.7834</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4797</v>
+        <v>0.17</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6765</v>
+        <v>-0.0037</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1968</v>
+        <v>0.1737</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.6778999999999999</v>
+        <v>1.0722</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. MOTLEY</t>
+          <t>C. MALCOLM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.65</v>
+        <v>1.4057</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.057</v>
+        <v>0.3384</v>
       </c>
       <c r="F20" t="n">
-        <v>1.707</v>
+        <v>1.0674</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.2773</v>
+        <v>-0.885</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0495</v>
+        <v>-0.6709000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.2279</v>
+        <v>-0.214</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.0837</v>
+        <v>0.2017</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6659</v>
+        <v>0.2017</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.7495000000000001</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1937</v>
+        <v>-1.0866</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7153</v>
+        <v>-0.8726</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4783</v>
+        <v>-0.214</v>
       </c>
       <c r="P20" t="n">
-        <v>1.6237</v>
+        <v>1.1598</v>
       </c>
       <c r="Q20" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R20" t="n">
-        <v>2.7834</v>
+        <v>2.3195</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2315</v>
+        <v>0.2005</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1142</v>
+        <v>0.2243</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1173</v>
+        <v>-0.0237</v>
       </c>
       <c r="V20" t="n">
-        <v>1.0722</v>
+        <v>0.9304</v>
       </c>
       <c r="W20" t="n">
         <v>1.0722</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5062</v>
+        <v>0.6407</v>
       </c>
       <c r="E21" t="n">
         <v>-0.2975</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8038</v>
+        <v>0.9382</v>
       </c>
       <c r="G21" t="n">
         <v>1.0401</v>
@@ -2092,13 +2092,13 @@
         <v>0.4639</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2091</v>
+        <v>-0.0747</v>
       </c>
       <c r="T21" t="n">
         <v>-0.2987</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0896</v>
+        <v>0.224</v>
       </c>
       <c r="V21" t="n">
         <v>-0.7886</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.9502</v>
+        <v>-0.5577</v>
       </c>
       <c r="E22" t="n">
         <v>-1.8387</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8884</v>
+        <v>1.2809</v>
       </c>
       <c r="G22" t="n">
         <v>0.9004</v>
@@ -2170,13 +2170,13 @@
         <v>1.3917</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2992</v>
+        <v>0.0934</v>
       </c>
       <c r="T22" t="n">
         <v>0.0395</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3387</v>
+        <v>0.0538</v>
       </c>
       <c r="V22" t="n">
         <v>0.5361</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.2259</v>
+        <v>-1.5689</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.7222</v>
+        <v>-3.1324</v>
       </c>
       <c r="F23" t="n">
-        <v>1.4963</v>
+        <v>1.5635</v>
       </c>
       <c r="G23" t="n">
         <v>0.2219</v>
@@ -2248,13 +2248,13 @@
         <v>1.3917</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3602</v>
+        <v>0.2967</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6721</v>
+        <v>-0.0824</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3119</v>
+        <v>0.3791</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.2897</v>
+        <v>-2.7063</v>
       </c>
       <c r="E24" t="n">
         <v>-5.4665</v>
       </c>
       <c r="F24" t="n">
-        <v>2.1768</v>
+        <v>2.7602</v>
       </c>
       <c r="G24" t="n">
         <v>-4.0055</v>
@@ -2326,13 +2326,13 @@
         <v>3.7112</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5008</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="T24" t="n">
         <v>-0.0351</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4657</v>
+        <v>0.1177</v>
       </c>
       <c r="V24" t="n">
         <v>2.1444</v>
@@ -2359,22 +2359,22 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>10.9646</v>
+        <v>12.5375</v>
       </c>
       <c r="E25" t="n">
         <v>-3.7361</v>
       </c>
       <c r="F25" t="n">
-        <v>14.7007</v>
+        <v>16.2734</v>
       </c>
       <c r="G25" t="n">
-        <v>2.597899999999999</v>
+        <v>2.5979</v>
       </c>
       <c r="H25" t="n">
-        <v>6.829899999999999</v>
+        <v>6.8299</v>
       </c>
       <c r="I25" t="n">
-        <v>-4.231999999999999</v>
+        <v>-4.232</v>
       </c>
       <c r="J25" t="n">
         <v>8.602799999999998</v>
@@ -2386,7 +2386,7 @@
         <v>-3.9154</v>
       </c>
       <c r="M25" t="n">
-        <v>-6.0048</v>
+        <v>-6.004799999999999</v>
       </c>
       <c r="N25" t="n">
         <v>-5.6884</v>
@@ -2404,13 +2404,13 @@
         <v>22.0354</v>
       </c>
       <c r="S25" t="n">
-        <v>1.0807</v>
+        <v>2.6533</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.01750000000000027</v>
+        <v>-0.01750000000000005</v>
       </c>
       <c r="U25" t="n">
-        <v>1.0982</v>
+        <v>2.6709</v>
       </c>
       <c r="V25" t="n">
         <v>4.9667</v>
